--- a/output/2026-09-01_08_Italia_Toscana_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-01_08_Italia_Toscana_Utensilerie_e_Macchine_Utensili.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,6 @@
           <t>Toscana Utensili S.r.l.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Firenze (FI)</t>
@@ -574,7 +573,6 @@
           <t>055 431651</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Utensileria, elettroutensili professionali (rivenditore ufficiale Festool). Verificata (elenco rivenditori Festool, Paginebianche). Sito web ed email non reperiti.</t>
@@ -582,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -624,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -666,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -708,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -718,7 +716,6 @@
           <t>3R Distribuzione di Ricciarelli Stefano</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Pistoia (PT)</t>
@@ -746,7 +743,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -788,7 +785,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -830,7 +827,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -840,7 +837,6 @@
           <t>Utensileria Lucchese S.r.l.</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>Lucca (LU)</t>
@@ -856,7 +852,6 @@
           <t>0583 341573</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Utensileria, viteria/bulloneria, articoli tecnici, macchine utensili (dettaglio e ingrosso). Verificata (Paginegialle, LEI Register, Foursquare). Telefono reperito da fonte pubblica (non presente nel dato grezzo). Sito web ed email non reperiti.</t>
@@ -864,7 +859,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -894,7 +889,6 @@
           <t>0587 486009</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Macchine utensili, taglio laser/plasma/getto d'acqua, lavorazione lamiera. Verificata (sito aziendale, Europages, Facebook). Attiva dal 1990. Email non reperita.</t>
@@ -902,7 +896,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -944,7 +938,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -974,7 +968,6 @@
           <t>0587 488190</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Macchine utensili per legno, plastica e leghe leggere. Verificata (sito aziendale, Kompass). ATTENZIONE: focus legno/plastica/leghe leggere, non metallo - verificare aderenza al target Dupuy. Email non reperita.</t>
@@ -1012,7 +1005,6 @@
           <t>0575 356815</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Forniture industriali, macchine utensili, utensileria. Verificata (Ufficio Camerale, Paginegialle). Attiva dal 1990, 6-9 dipendenti. Email non reperita.</t>
@@ -1020,7 +1012,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1042,6 @@
           <t>+39 3928000358</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Utensili e attrezzature industriali/artigianali (meccanico, autofficina, gommista, carrozzeria). Verificata (sito aziendale, Facebook). Ha acquisito MCA nel 2023. Email non reperita.</t>
@@ -1058,7 +1049,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1101,6 @@
           <t>Polytechnica di Bagnai Danny</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>Siena (SI)</t>
@@ -1126,7 +1116,6 @@
           <t>0577 938135</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Articoli tecnici per lavorazione meccanica, utensili, strumenti di misura (dettaglio e ingrosso). Verificata (iCribis, Ufficio Camerale). Ditta individuale, 2-5 addetti. Sito web ed email non reperiti.</t>
@@ -1206,7 +1195,6 @@
           <t>+39 0564 418903</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>Forniture industriali, noleggio compressori/generatori, installazione macchinari industriali. Verificata (Ufficio Camerale, sito aziendale). Attiva dal 1972, 11 dipendenti. Email fornita non confermata (dominio diverso), lasciata vuota. Focus più ampio su impiantistica/energia che utensileria in senso stretto.</t>
@@ -1239,8 +1227,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>Componenti industriali e accessori da officina; core business ricambi per macchine agricole/rimorchi (dealer New Holland dal 2000). Verificata (sito aziendale). ATTENZIONE: sezione industriale/officina marginale rispetto al core business agricolo - target parzialmente disallineato.</t>
@@ -1273,8 +1259,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>Forniture industriali, cuscinetti, utensili manuali/elettrici, tecnica industriale. Verificata (sito aziendale, Virgilio). Attiva dal 1945, serve anche province di Pisa e Grosseto. Telefono/email non reperiti pubblicamente.</t>
